--- a/data/trans_dic/P19C03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C03-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por un empaste</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por un empaste (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,52; 40,99</t>
+          <t>32,82; 41,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,01; 31,43</t>
+          <t>24,28; 31,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,64; 33,81</t>
+          <t>26,29; 34,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,92; 28,44</t>
+          <t>19,64; 27,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,47; 39,4</t>
+          <t>31,93; 39,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,71; 30,77</t>
+          <t>23,61; 30,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,34; 29,64</t>
+          <t>22,51; 29,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,34; 20,28</t>
+          <t>15,32; 20,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,56; 39,58</t>
+          <t>33,12; 39,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,04; 30,21</t>
+          <t>24,97; 30,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,25; 30,7</t>
+          <t>25,11; 30,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,37; 23,23</t>
+          <t>18,4; 23,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,57; 33,43</t>
+          <t>26,19; 33,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,67; 35,16</t>
+          <t>28,55; 35,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,27; 29,68</t>
+          <t>23,02; 29,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 17,53</t>
+          <t>6,94; 17,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,75; 36,55</t>
+          <t>29,53; 36,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,27; 33,44</t>
+          <t>27,35; 33,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,59; 29,45</t>
+          <t>23,5; 29,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,55; 19,83</t>
+          <t>15,22; 19,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,85; 34,15</t>
+          <t>28,73; 33,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,86; 33,4</t>
+          <t>28,55; 33,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,36; 28,5</t>
+          <t>24,26; 28,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 17,41</t>
+          <t>9,57; 17,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,77; 39,86</t>
+          <t>31,47; 39,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,92; 34,65</t>
+          <t>26,98; 34,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,26; 37,62</t>
+          <t>29,19; 37,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,7; 28,51</t>
+          <t>20,58; 28,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,64; 36,16</t>
+          <t>28,7; 36,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,83; 34,46</t>
+          <t>26,62; 34,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,08; 35,74</t>
+          <t>27,89; 36,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 29,03</t>
+          <t>9,83; 29,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,11; 36,84</t>
+          <t>31,45; 37,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,97; 33,22</t>
+          <t>28,1; 33,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,76; 35,42</t>
+          <t>29,61; 35,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 26,95</t>
+          <t>14,39; 26,64</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,84; 31,49</t>
+          <t>24,68; 31,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,0; 32,28</t>
+          <t>26,17; 32,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,68; 26,54</t>
+          <t>20,63; 26,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,25; 18,73</t>
+          <t>13,12; 18,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,58; 31,74</t>
+          <t>25,22; 31,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,42; 31,28</t>
+          <t>25,15; 31,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,65; 25,4</t>
+          <t>19,99; 25,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 17,08</t>
+          <t>11,96; 17,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,13; 30,71</t>
+          <t>26,01; 30,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,64; 30,61</t>
+          <t>26,46; 30,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,94; 25,18</t>
+          <t>20,86; 24,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 17,03</t>
+          <t>13,23; 17,03</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,08; 34,04</t>
+          <t>30,09; 33,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,16; 31,77</t>
+          <t>28,27; 31,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,65; 29,28</t>
+          <t>25,99; 29,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,9; 20,19</t>
+          <t>13,8; 20,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,12; 33,87</t>
+          <t>30,36; 33,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,05; 30,57</t>
+          <t>27,43; 30,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,66; 27,87</t>
+          <t>24,69; 28,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,48; 19,96</t>
+          <t>14,53; 19,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,72; 33,28</t>
+          <t>30,82; 33,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,31; 30,8</t>
+          <t>28,31; 30,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,65; 28,05</t>
+          <t>25,61; 28,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,26; 19,35</t>
+          <t>15,51; 19,38</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por un empaste</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por un empaste (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>155386; 195856</t>
+          <t>156846; 198722</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145470; 190447</t>
+          <t>147115; 193737</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134633; 177499</t>
+          <t>138002; 179891</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121799; 173874</t>
+          <t>120051; 170868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>169360; 212000</t>
+          <t>171790; 213906</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>150778; 195633</t>
+          <t>150101; 195578</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>121590; 161339</t>
+          <t>122557; 162529</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99837; 131982</t>
+          <t>99724; 131499</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>340918; 402085</t>
+          <t>336449; 398226</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>310934; 375188</t>
+          <t>310080; 373436</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>270008; 328279</t>
+          <t>268539; 327772</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>231844; 293221</t>
+          <t>232280; 296589</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>191899; 241382</t>
+          <t>189105; 243728</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>248310; 304475</t>
+          <t>247251; 304877</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>189983; 242267</t>
+          <t>187950; 238299</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73578; 204474</t>
+          <t>80951; 206402</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>239228; 293946</t>
+          <t>237471; 291624</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>244849; 300327</t>
+          <t>245588; 303280</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>204362; 255168</t>
+          <t>203633; 255950</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>146491; 186908</t>
+          <t>143453; 184956</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>440346; 521219</t>
+          <t>438565; 515312</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>509074; 589259</t>
+          <t>503687; 592540</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>409843; 479570</t>
+          <t>408301; 480163</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>204262; 367143</t>
+          <t>201810; 372456</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>172826; 216864</t>
+          <t>171217; 215527</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>170945; 220060</t>
+          <t>171342; 221930</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>161037; 207041</t>
+          <t>160641; 207110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142068; 195665</t>
+          <t>141203; 195483</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>167438; 211377</t>
+          <t>167768; 213814</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>181757; 233449</t>
+          <t>180374; 230478</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>162767; 207218</t>
+          <t>161669; 209237</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>90116; 267716</t>
+          <t>90674; 270877</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>351169; 415799</t>
+          <t>354982; 418333</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>367136; 435982</t>
+          <t>368812; 438762</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>336366; 400239</t>
+          <t>334663; 399086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>221009; 433462</t>
+          <t>231473; 428507</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>176255; 223479</t>
+          <t>175152; 222769</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>209240; 259805</t>
+          <t>210598; 262650</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>159752; 205085</t>
+          <t>159367; 207325</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>117747; 166453</t>
+          <t>116655; 165081</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>208256; 258392</t>
+          <t>205262; 258560</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>237261; 291906</t>
+          <t>234697; 291349</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>172308; 222718</t>
+          <t>175280; 227341</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>126143; 181574</t>
+          <t>127122; 180957</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>398130; 467875</t>
+          <t>396263; 462452</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>463007; 531962</t>
+          <t>459794; 536475</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>345335; 415337</t>
+          <t>344112; 411993</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>258435; 332404</t>
+          <t>258175; 332381</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>738000; 835283</t>
+          <t>738252; 831122</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>819942; 925148</t>
+          <t>823239; 931331</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>683521; 780111</t>
+          <t>692520; 783155</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>466080; 677159</t>
+          <t>462873; 672309</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>825485; 928483</t>
+          <t>832173; 926843</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>850603; 961140</t>
+          <t>862414; 965794</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>707216; 799085</t>
+          <t>707993; 804134</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>518144; 714249</t>
+          <t>520003; 711757</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1595910; 1728616</t>
+          <t>1600758; 1731109</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1714774; 1865452</t>
+          <t>1714290; 1857413</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1419039; 1551376</t>
+          <t>1416417; 1558872</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1057834; 1341274</t>
+          <t>1075093; 1342961</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C03-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,82; 41,59</t>
+          <t>32,94; 41,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,28; 31,97</t>
+          <t>24,67; 31,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,29; 34,27</t>
+          <t>26,01; 34,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,64; 27,95</t>
+          <t>19,4; 27,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,93; 39,75</t>
+          <t>32,05; 39,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,61; 30,76</t>
+          <t>23,73; 30,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,51; 29,86</t>
+          <t>22,33; 29,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,32; 20,2</t>
+          <t>15,76; 20,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,12; 39,2</t>
+          <t>33,72; 39,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,97; 30,07</t>
+          <t>24,91; 30,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,11; 30,65</t>
+          <t>24,97; 30,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,4; 23,5</t>
+          <t>18,18; 22,7</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,19; 33,75</t>
+          <t>26,19; 33,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,55; 35,2</t>
+          <t>28,68; 35,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,02; 29,19</t>
+          <t>23,12; 29,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 17,69</t>
+          <t>14,3; 19,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,53; 36,26</t>
+          <t>29,56; 36,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,35; 33,77</t>
+          <t>27,22; 33,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,5; 29,54</t>
+          <t>23,64; 29,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 19,63</t>
+          <t>15,58; 19,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,73; 33,76</t>
+          <t>29,1; 34,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,55; 33,59</t>
+          <t>28,67; 33,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,26; 28,53</t>
+          <t>24,48; 29,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 17,66</t>
+          <t>15,46; 18,7</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,47; 39,62</t>
+          <t>31,25; 39,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,98; 34,95</t>
+          <t>27,09; 34,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,19; 37,63</t>
+          <t>29,18; 37,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,58; 28,48</t>
+          <t>20,28; 27,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 36,57</t>
+          <t>28,77; 36,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,62; 34,02</t>
+          <t>26,49; 33,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,89; 36,09</t>
+          <t>28,39; 35,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 29,38</t>
+          <t>20,13; 25,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,45; 37,06</t>
+          <t>31,18; 36,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,1; 33,43</t>
+          <t>28,03; 33,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,61; 35,31</t>
+          <t>29,75; 35,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,39; 26,64</t>
+          <t>21,15; 25,6</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,68; 31,39</t>
+          <t>24,58; 31,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,17; 32,64</t>
+          <t>26,16; 32,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,63; 26,83</t>
+          <t>20,45; 26,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,12; 18,57</t>
+          <t>12,7; 17,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,22; 31,76</t>
+          <t>25,34; 31,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,15; 31,22</t>
+          <t>24,94; 31,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,99; 25,93</t>
+          <t>19,24; 25,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,96; 17,02</t>
+          <t>14,14; 18,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,01; 30,35</t>
+          <t>26,12; 30,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,46; 30,87</t>
+          <t>26,36; 30,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,86; 24,98</t>
+          <t>20,88; 25,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,23; 17,03</t>
+          <t>14,2; 17,23</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,09; 33,87</t>
+          <t>30,02; 33,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,27; 31,98</t>
+          <t>28,35; 31,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,99; 29,39</t>
+          <t>25,68; 29,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,8; 20,05</t>
+          <t>17,63; 20,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,36; 33,81</t>
+          <t>30,17; 33,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,43; 30,71</t>
+          <t>27,38; 30,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,69; 28,04</t>
+          <t>24,67; 27,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,53; 19,89</t>
+          <t>17,27; 19,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,82; 33,32</t>
+          <t>30,61; 33,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,31; 30,67</t>
+          <t>28,23; 30,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,61; 28,18</t>
+          <t>25,74; 28,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,51; 19,38</t>
+          <t>17,79; 19,76</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143481</t>
+          <t>151784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>116483</t>
+          <t>127243</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>259964</t>
+          <t>279026</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>156846; 198722</t>
+          <t>157385; 199305</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>147115; 193737</t>
+          <t>149509; 192608</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>138002; 179891</t>
+          <t>136546; 179853</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120051; 170868</t>
+          <t>127969; 181437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>171790; 213906</t>
+          <t>172445; 213511</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>150101; 195578</t>
+          <t>150886; 196587</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>122557; 162529</t>
+          <t>121540; 163166</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99724; 131499</t>
+          <t>111195; 146292</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>336449; 398226</t>
+          <t>342597; 400160</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>310080; 373436</t>
+          <t>309374; 375645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>268539; 327772</t>
+          <t>266979; 328397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>232280; 296589</t>
+          <t>248219; 309813</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>152351</t>
+          <t>168371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>164946</t>
+          <t>184125</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>317297</t>
+          <t>352496</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>189105; 243728</t>
+          <t>189114; 241296</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>247251; 304877</t>
+          <t>248362; 305684</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>187950; 238299</t>
+          <t>188767; 240135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80951; 206402</t>
+          <t>145267; 199964</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>237471; 291624</t>
+          <t>237723; 292767</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>245588; 303280</t>
+          <t>244448; 298428</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>203633; 255950</t>
+          <t>204813; 257415</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>143453; 184956</t>
+          <t>163242; 206943</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>438565; 515312</t>
+          <t>444229; 522495</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>503687; 592540</t>
+          <t>505764; 584558</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>408301; 480163</t>
+          <t>411944; 488030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>201810; 372456</t>
+          <t>319005; 385863</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166545</t>
+          <t>184837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>185598</t>
+          <t>180170</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>352142</t>
+          <t>365007</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>171217; 215527</t>
+          <t>170040; 217434</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>171342; 221930</t>
+          <t>172034; 218564</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>160641; 207110</t>
+          <t>160618; 208095</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141203; 195483</t>
+          <t>156973; 213249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>167768; 213814</t>
+          <t>168188; 212008</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>180374; 230478</t>
+          <t>179455; 229454</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>161669; 209237</t>
+          <t>164597; 207998</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>90674; 270877</t>
+          <t>160130; 204777</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>354982; 418333</t>
+          <t>351885; 416159</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>368812; 438762</t>
+          <t>367981; 437717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>334663; 399086</t>
+          <t>336214; 400345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>231473; 428507</t>
+          <t>331964; 401687</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139312</t>
+          <t>144312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>157140</t>
+          <t>172549</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>296452</t>
+          <t>316861</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>175152; 222769</t>
+          <t>174446; 221050</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>210598; 262650</t>
+          <t>210521; 262078</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>159367; 207325</t>
+          <t>157983; 203690</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>116655; 165081</t>
+          <t>120206; 169780</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>205262; 258560</t>
+          <t>206296; 259134</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>234697; 291349</t>
+          <t>232726; 291442</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>175280; 227341</t>
+          <t>168700; 222700</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>127122; 180957</t>
+          <t>152137; 194353</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>396263; 462452</t>
+          <t>398051; 466648</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>459794; 536475</t>
+          <t>458119; 532459</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>344112; 411993</t>
+          <t>344458; 412421</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>258175; 332381</t>
+          <t>287190; 348604</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>601689</t>
+          <t>649304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>624166</t>
+          <t>664087</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1225855</t>
+          <t>1313391</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>738252; 831122</t>
+          <t>736551; 833872</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>823239; 931331</t>
+          <t>825376; 926135</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>692520; 783155</t>
+          <t>684125; 781855</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>462873; 672309</t>
+          <t>598651; 706277</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>832173; 926843</t>
+          <t>826844; 928824</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>862414; 965794</t>
+          <t>861046; 965161</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>707993; 804134</t>
+          <t>707403; 799371</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>520003; 711757</t>
+          <t>626031; 708473</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1600758; 1731109</t>
+          <t>1590088; 1727432</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1714290; 1857413</t>
+          <t>1709631; 1859926</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1416417; 1558872</t>
+          <t>1423747; 1555652</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1075093; 1342961</t>
+          <t>1248757; 1387336</t>
         </is>
       </c>
     </row>
